--- a/dados/TabelaBrasileirao.xlsx
+++ b/dados/TabelaBrasileirao.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,42 +417,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Posição</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Pontos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Jogos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Vitorias</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Empates</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Derrotas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Saldo de Gols</t>
         </is>
@@ -476,26 +464,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -504,17 +492,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -523,7 +511,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -532,26 +520,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -560,26 +548,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -588,26 +576,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -616,26 +604,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -644,26 +632,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -672,26 +660,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Paranaense</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -700,26 +688,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -728,20 +716,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -756,20 +744,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -784,26 +772,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -812,26 +800,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -840,26 +828,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="16">
@@ -868,26 +856,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17">
@@ -896,26 +884,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="18">
@@ -924,26 +912,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -952,26 +940,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Clube do Remo</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="20">
@@ -980,26 +968,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="21">
@@ -1008,14 +996,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1024,10 +1012,10 @@
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
   </sheetData>
